--- a/etc/symbol_wingdings_4sheets_unicode_mapped.xlsx
+++ b/etc/symbol_wingdings_4sheets_unicode_mapped.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\hidek\git\wmf2svg\etc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52ED0423-FA50-437E-9D81-152531053BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7007D7F6-6E1C-4428-8EEB-6640D6E2D39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4100" yWindow="4100" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Symbol" sheetId="1" r:id="rId1"/>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3202" uniqueCount="1948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3202" uniqueCount="1942">
   <si>
     <t>Code(Hex)</t>
   </si>
@@ -1816,34 +1816,16 @@
     <t>Ò</t>
   </si>
   <si>
-    <t>U+F6DA</t>
-  </si>
-  <si>
-    <t></t>
-  </si>
-  <si>
     <t>0xD3</t>
   </si>
   <si>
     <t>Ó</t>
   </si>
   <si>
-    <t>U+F6D9</t>
-  </si>
-  <si>
-    <t></t>
-  </si>
-  <si>
     <t>0xD4</t>
   </si>
   <si>
     <t>Ô</t>
-  </si>
-  <si>
-    <t>U+F6DB</t>
-  </si>
-  <si>
-    <t></t>
   </si>
   <si>
     <t>0xD5</t>
@@ -7074,13 +7056,13 @@
         <v>198</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>1886</v>
+        <v>1880</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>1888</v>
+        <v>1882</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -7830,13 +7812,13 @@
         <v>481</v>
       </c>
       <c r="B90" s="20" t="s">
-        <v>1889</v>
+        <v>1883</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>1891</v>
+        <v>1885</v>
       </c>
       <c r="D90" s="21" t="s">
-        <v>1890</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -7847,10 +7829,10 @@
         <v>484</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>1893</v>
+        <v>1887</v>
       </c>
       <c r="D91" s="22" t="s">
-        <v>1892</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -8126,92 +8108,92 @@
       <c r="B111" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>564</v>
+      <c r="C111" s="15" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D111" s="14" t="s">
+        <v>1873</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>566</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="D112" s="7" t="s">
-        <v>568</v>
+        <v>564</v>
+      </c>
+      <c r="C112" s="17" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D112" s="16" t="s">
+        <v>1875</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>572</v>
+        <v>566</v>
+      </c>
+      <c r="C113" s="15" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D113" s="14" t="s">
+        <v>1877</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>450</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>420</v>
@@ -8219,520 +8201,520 @@
     </row>
     <row r="118" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>1880</v>
+        <v>1874</v>
       </c>
       <c r="D127" s="14" t="s">
-        <v>1879</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="C128" s="17" t="s">
-        <v>1882</v>
+        <v>1876</v>
       </c>
       <c r="D128" s="16" t="s">
-        <v>1881</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>1885</v>
+        <v>1879</v>
       </c>
       <c r="D129" s="14" t="s">
-        <v>1883</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C130" s="17" t="s">
-        <v>1884</v>
+        <v>1878</v>
       </c>
       <c r="D130" s="7" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>1910</v>
+        <v>1904</v>
       </c>
       <c r="D131" s="23" t="s">
-        <v>1895</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C132" s="17" t="s">
-        <v>1912</v>
+        <v>1906</v>
       </c>
       <c r="D132" s="24" t="s">
-        <v>1896</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>1911</v>
+        <v>1905</v>
       </c>
       <c r="D133" s="23" t="s">
-        <v>1897</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="5" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C134" s="17" t="s">
-        <v>1907</v>
+        <v>1901</v>
       </c>
       <c r="D134" s="24" t="s">
-        <v>1898</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>1908</v>
+        <v>1902</v>
       </c>
       <c r="D135" s="23" t="s">
-        <v>1899</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="5" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="C136" s="17" t="s">
-        <v>1909</v>
+        <v>1903</v>
       </c>
       <c r="D136" s="24" t="s">
-        <v>1900</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>1922</v>
+        <v>1916</v>
       </c>
       <c r="D137" s="23" t="s">
-        <v>1919</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="5" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C138" s="17" t="s">
-        <v>1923</v>
+        <v>1917</v>
       </c>
       <c r="D138" s="24" t="s">
-        <v>1920</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>1925</v>
+        <v>1919</v>
       </c>
       <c r="D139" s="23" t="s">
-        <v>1921</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="17" t="s">
-        <v>1894</v>
+        <v>1888</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="C140" s="17" t="s">
-        <v>1924</v>
+        <v>1918</v>
       </c>
       <c r="D140" s="24" t="s">
-        <v>1926</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="5" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="C143" s="17" t="s">
-        <v>1933</v>
+        <v>1927</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="C144" s="17" t="s">
-        <v>1924</v>
+        <v>1918</v>
       </c>
       <c r="D144" s="24" t="s">
-        <v>1926</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="5" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>1918</v>
+        <v>1912</v>
       </c>
       <c r="D146" s="23" t="s">
-        <v>1913</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="5" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>465</v>
       </c>
       <c r="C147" s="17" t="s">
-        <v>1917</v>
+        <v>1911</v>
       </c>
       <c r="D147" s="24" t="s">
-        <v>1914</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>1916</v>
+        <v>1910</v>
       </c>
       <c r="D148" s="23" t="s">
-        <v>1915</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="5" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="C149" s="17" t="s">
-        <v>1904</v>
+        <v>1898</v>
       </c>
       <c r="D149" s="24" t="s">
-        <v>1901</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>1905</v>
+        <v>1899</v>
       </c>
       <c r="D150" s="23" t="s">
-        <v>1902</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="5" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="C151" s="17" t="s">
-        <v>1906</v>
+        <v>1900</v>
       </c>
       <c r="D151" s="24" t="s">
-        <v>1903</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>1930</v>
+        <v>1924</v>
       </c>
       <c r="D152" s="23" t="s">
-        <v>1927</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="5" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="C153" s="17" t="s">
-        <v>1931</v>
+        <v>1925</v>
       </c>
       <c r="D153" s="24" t="s">
-        <v>1928</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>1932</v>
+        <v>1926</v>
       </c>
       <c r="D154" s="23" t="s">
-        <v>1929</v>
+        <v>1923</v>
       </c>
     </row>
   </sheetData>
@@ -8759,7 +8741,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1934</v>
+        <v>1928</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -8776,10 +8758,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -8790,10 +8772,10 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -8804,10 +8786,10 @@
         <v>11</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -8818,10 +8800,10 @@
         <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -8832,10 +8814,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -8846,10 +8828,10 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -8860,10 +8842,10 @@
         <v>21</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -8874,10 +8856,10 @@
         <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -8888,10 +8870,10 @@
         <v>27</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -8902,10 +8884,10 @@
         <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -8916,10 +8898,10 @@
         <v>33</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -8930,10 +8912,10 @@
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -8944,10 +8926,10 @@
         <v>37</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -8958,10 +8940,10 @@
         <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -8972,10 +8954,10 @@
         <v>43</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -8986,10 +8968,10 @@
         <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9000,10 +8982,10 @@
         <v>47</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9014,10 +8996,10 @@
         <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9028,10 +9010,10 @@
         <v>51</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9042,10 +9024,10 @@
         <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9056,10 +9038,10 @@
         <v>55</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9070,10 +9052,10 @@
         <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9084,10 +9066,10 @@
         <v>59</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9098,10 +9080,10 @@
         <v>61</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9112,10 +9094,10 @@
         <v>63</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9126,10 +9108,10 @@
         <v>65</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9140,10 +9122,10 @@
         <v>67</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9154,10 +9136,10 @@
         <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9168,10 +9150,10 @@
         <v>71</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9182,10 +9164,10 @@
         <v>73</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9196,10 +9178,10 @@
         <v>75</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9210,10 +9192,10 @@
         <v>77</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9224,10 +9206,10 @@
         <v>81</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9238,10 +9220,10 @@
         <v>85</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9252,10 +9234,10 @@
         <v>89</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9266,10 +9248,10 @@
         <v>93</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9280,10 +9262,10 @@
         <v>97</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9294,10 +9276,10 @@
         <v>101</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9308,10 +9290,10 @@
         <v>105</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9322,10 +9304,10 @@
         <v>109</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9336,10 +9318,10 @@
         <v>113</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9350,10 +9332,10 @@
         <v>117</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9364,10 +9346,10 @@
         <v>121</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9378,10 +9360,10 @@
         <v>125</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9392,10 +9374,10 @@
         <v>129</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9406,10 +9388,10 @@
         <v>133</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9420,10 +9402,10 @@
         <v>137</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9434,10 +9416,10 @@
         <v>141</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9448,10 +9430,10 @@
         <v>145</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9462,10 +9444,10 @@
         <v>149</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9476,10 +9458,10 @@
         <v>153</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9490,10 +9472,10 @@
         <v>157</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9504,10 +9486,10 @@
         <v>161</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9518,10 +9500,10 @@
         <v>165</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9532,10 +9514,10 @@
         <v>169</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9546,10 +9528,10 @@
         <v>173</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9560,10 +9542,10 @@
         <v>177</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9574,10 +9556,10 @@
         <v>181</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9588,10 +9570,10 @@
         <v>185</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9602,10 +9584,10 @@
         <v>187</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9616,10 +9598,10 @@
         <v>191</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9630,10 +9612,10 @@
         <v>193</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9644,10 +9626,10 @@
         <v>197</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9658,10 +9640,10 @@
         <v>199</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9672,10 +9654,10 @@
         <v>201</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9686,10 +9668,10 @@
         <v>205</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9700,10 +9682,10 @@
         <v>209</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9714,10 +9696,10 @@
         <v>213</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9728,10 +9710,10 @@
         <v>217</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9742,10 +9724,10 @@
         <v>221</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9756,10 +9738,10 @@
         <v>225</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9770,10 +9752,10 @@
         <v>229</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9784,10 +9766,10 @@
         <v>233</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9798,10 +9780,10 @@
         <v>237</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9812,10 +9794,10 @@
         <v>241</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9826,10 +9808,10 @@
         <v>245</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9840,10 +9822,10 @@
         <v>249</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9854,10 +9836,10 @@
         <v>253</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9868,10 +9850,10 @@
         <v>257</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9882,10 +9864,10 @@
         <v>261</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9896,10 +9878,10 @@
         <v>265</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9910,10 +9892,10 @@
         <v>269</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9924,10 +9906,10 @@
         <v>273</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9938,10 +9920,10 @@
         <v>277</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9952,10 +9934,10 @@
         <v>281</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9966,10 +9948,10 @@
         <v>285</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9980,10 +9962,10 @@
         <v>289</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -9994,10 +9976,10 @@
         <v>293</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10008,10 +9990,10 @@
         <v>297</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10022,10 +10004,10 @@
         <v>301</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10036,10 +10018,10 @@
         <v>305</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10050,10 +10032,10 @@
         <v>307</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10064,10 +10046,10 @@
         <v>309</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10078,10 +10060,10 @@
         <v>311</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10092,10 +10074,10 @@
         <v>316</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10103,13 +10085,13 @@
         <v>317</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>1935</v>
+        <v>1929</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10120,10 +10102,10 @@
         <v>319</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10134,10 +10116,10 @@
         <v>321</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10148,10 +10130,10 @@
         <v>323</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10162,10 +10144,10 @@
         <v>325</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10176,10 +10158,10 @@
         <v>327</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10190,10 +10172,10 @@
         <v>329</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10204,10 +10186,10 @@
         <v>331</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10218,10 +10200,10 @@
         <v>333</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10232,10 +10214,10 @@
         <v>335</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10246,10 +10228,10 @@
         <v>337</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10260,10 +10242,10 @@
         <v>339</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10271,13 +10253,13 @@
         <v>340</v>
       </c>
       <c r="B109" s="25" t="s">
-        <v>1936</v>
+        <v>1930</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10288,10 +10270,10 @@
         <v>342</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10299,13 +10281,13 @@
         <v>343</v>
       </c>
       <c r="B111" s="25" t="s">
-        <v>1937</v>
+        <v>1931</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10313,13 +10295,13 @@
         <v>344</v>
       </c>
       <c r="B112" s="26" t="s">
-        <v>1938</v>
+        <v>1932</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10330,10 +10312,10 @@
         <v>346</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10344,10 +10326,10 @@
         <v>348</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10358,10 +10340,10 @@
         <v>350</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10372,10 +10354,10 @@
         <v>352</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10386,10 +10368,10 @@
         <v>354</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10400,10 +10382,10 @@
         <v>356</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>1940</v>
+        <v>1934</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10414,10 +10396,10 @@
         <v>358</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10428,10 +10410,10 @@
         <v>360</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10442,10 +10424,10 @@
         <v>362</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10456,10 +10438,10 @@
         <v>364</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10470,10 +10452,10 @@
         <v>366</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10484,10 +10466,10 @@
         <v>368</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10495,13 +10477,13 @@
         <v>369</v>
       </c>
       <c r="B125" s="25" t="s">
-        <v>1939</v>
+        <v>1933</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10512,7 +10494,7 @@
         <v>371</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>460</v>
@@ -10540,10 +10522,10 @@
         <v>375</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10554,10 +10536,10 @@
         <v>377</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10568,10 +10550,10 @@
         <v>381</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10582,10 +10564,10 @@
         <v>385</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10596,10 +10578,10 @@
         <v>389</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10610,10 +10592,10 @@
         <v>393</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10624,10 +10606,10 @@
         <v>397</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10638,10 +10620,10 @@
         <v>400</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10652,10 +10634,10 @@
         <v>404</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10666,10 +10648,10 @@
         <v>408</v>
       </c>
       <c r="C137" s="17" t="s">
-        <v>1941</v>
+        <v>1935</v>
       </c>
       <c r="D137" s="24" t="s">
-        <v>1943</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10680,10 +10662,10 @@
         <v>412</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>1942</v>
+        <v>1936</v>
       </c>
       <c r="D138" s="27" t="s">
-        <v>1944</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10694,10 +10676,10 @@
         <v>416</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10708,10 +10690,10 @@
         <v>420</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10722,10 +10704,10 @@
         <v>424</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10736,10 +10718,10 @@
         <v>428</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10750,10 +10732,10 @@
         <v>432</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10764,10 +10746,10 @@
         <v>436</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10778,10 +10760,10 @@
         <v>438</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10792,10 +10774,10 @@
         <v>440</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10806,10 +10788,10 @@
         <v>444</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10820,10 +10802,10 @@
         <v>448</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10834,10 +10816,10 @@
         <v>452</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10848,10 +10830,10 @@
         <v>456</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10862,10 +10844,10 @@
         <v>460</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10876,10 +10858,10 @@
         <v>463</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10890,10 +10872,10 @@
         <v>467</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10904,10 +10886,10 @@
         <v>471</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10918,10 +10900,10 @@
         <v>475</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10932,10 +10914,10 @@
         <v>479</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10946,10 +10928,10 @@
         <v>482</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="D157" s="7" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10960,10 +10942,10 @@
         <v>484</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10974,10 +10956,10 @@
         <v>486</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -10988,10 +10970,10 @@
         <v>490</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11002,10 +10984,10 @@
         <v>494</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11016,10 +10998,10 @@
         <v>498</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11030,10 +11012,10 @@
         <v>502</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11044,10 +11026,10 @@
         <v>506</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11058,10 +11040,10 @@
         <v>510</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="D165" s="7" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11072,10 +11054,10 @@
         <v>514</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11086,10 +11068,10 @@
         <v>518</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11100,10 +11082,10 @@
         <v>522</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11114,10 +11096,10 @@
         <v>526</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="D169" s="7" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11128,10 +11110,10 @@
         <v>530</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11142,10 +11124,10 @@
         <v>534</v>
       </c>
       <c r="C171" s="17" t="s">
-        <v>1945</v>
+        <v>1939</v>
       </c>
       <c r="D171" s="16" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11156,10 +11138,10 @@
         <v>538</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11170,10 +11152,10 @@
         <v>542</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="D173" s="7" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11184,10 +11166,10 @@
         <v>546</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11198,10 +11180,10 @@
         <v>550</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="D175" s="7" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11212,10 +11194,10 @@
         <v>554</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11226,10 +11208,10 @@
         <v>558</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="D177" s="7" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11240,637 +11222,637 @@
         <v>562</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B179" s="9" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="D179" s="7" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="B180" s="8" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="5" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="B181" s="9" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="D181" s="7" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="5" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="B183" s="9" t="s">
         <v>450</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="D183" s="7" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="5" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="B185" s="9" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="D185" s="7" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="5" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B187" s="9" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="D187" s="7" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="5" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="D189" s="7" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="B190" s="8" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="5" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="D191" s="7" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="B192" s="8" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="5" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="B194" s="8" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="5" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="D195" s="7" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="5" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="D197" s="7" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="B198" s="8" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="5" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="D199" s="7" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="B200" s="8" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="5" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="D201" s="7" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="B202" s="8" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="5" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="D203" s="7" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="B204" s="8" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="5" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="D205" s="7" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="B206" s="8" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="5" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="D207" s="7" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="B208" s="8" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="5" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
       <c r="D209" s="7" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="5" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="D211" s="7" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="5" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="D213" s="7" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="5" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="B215" s="9" t="s">
         <v>465</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="D215" s="7" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="B216" s="8" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="5" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="D217" s="7" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="5" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>1117</v>
+        <v>1111</v>
       </c>
       <c r="D219" s="7" t="s">
-        <v>1118</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="B220" s="8" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>1119</v>
+        <v>1113</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="5" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
       <c r="D221" s="7" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="B222" s="8" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="5" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="C223" s="17" t="s">
-        <v>1947</v>
+        <v>1941</v>
       </c>
       <c r="D223" s="7"/>
     </row>
@@ -11898,7 +11880,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -11915,10 +11897,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11929,10 +11911,10 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11943,10 +11925,10 @@
         <v>11</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11957,10 +11939,10 @@
         <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11971,10 +11953,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11985,10 +11967,10 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>1137</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -11999,10 +11981,10 @@
         <v>21</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1138</v>
+        <v>1132</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12013,10 +11995,10 @@
         <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12027,10 +12009,10 @@
         <v>27</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1142</v>
+        <v>1136</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1143</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12041,10 +12023,10 @@
         <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1145</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12055,10 +12037,10 @@
         <v>33</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1147</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12069,10 +12051,10 @@
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>1149</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12083,10 +12065,10 @@
         <v>37</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12097,10 +12079,10 @@
         <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12111,10 +12093,10 @@
         <v>43</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12125,10 +12107,10 @@
         <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12139,10 +12121,10 @@
         <v>47</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1159</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12153,10 +12135,10 @@
         <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1160</v>
+        <v>1154</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12167,10 +12149,10 @@
         <v>51</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1163</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12181,10 +12163,10 @@
         <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1164</v>
+        <v>1158</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12195,10 +12177,10 @@
         <v>55</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12209,10 +12191,10 @@
         <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1168</v>
+        <v>1162</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>1169</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12223,10 +12205,10 @@
         <v>59</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12237,10 +12219,10 @@
         <v>61</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>1173</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12251,10 +12233,10 @@
         <v>63</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>1174</v>
+        <v>1168</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12265,10 +12247,10 @@
         <v>65</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>1177</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12279,10 +12261,10 @@
         <v>67</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1179</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12293,10 +12275,10 @@
         <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1180</v>
+        <v>1174</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12307,10 +12289,10 @@
         <v>71</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>1182</v>
+        <v>1176</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12321,10 +12303,10 @@
         <v>73</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12335,10 +12317,10 @@
         <v>75</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12349,10 +12331,10 @@
         <v>77</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12363,10 +12345,10 @@
         <v>81</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1191</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12377,10 +12359,10 @@
         <v>85</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12391,10 +12373,10 @@
         <v>89</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12405,10 +12387,10 @@
         <v>93</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12419,10 +12401,10 @@
         <v>97</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12433,10 +12415,10 @@
         <v>101</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12447,10 +12429,10 @@
         <v>105</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12461,10 +12443,10 @@
         <v>109</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12475,10 +12457,10 @@
         <v>113</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12489,10 +12471,10 @@
         <v>117</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12503,10 +12485,10 @@
         <v>121</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12517,10 +12499,10 @@
         <v>125</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12531,10 +12513,10 @@
         <v>129</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12545,10 +12527,10 @@
         <v>133</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>1217</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12559,10 +12541,10 @@
         <v>137</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12573,10 +12555,10 @@
         <v>141</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1220</v>
+        <v>1214</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12587,10 +12569,10 @@
         <v>145</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1223</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12601,10 +12583,10 @@
         <v>149</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12615,10 +12597,10 @@
         <v>153</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>1226</v>
+        <v>1220</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1227</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12629,10 +12611,10 @@
         <v>157</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>1226</v>
+        <v>1220</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>1227</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12643,10 +12625,10 @@
         <v>161</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12657,10 +12639,10 @@
         <v>165</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12671,10 +12653,10 @@
         <v>169</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12685,10 +12667,10 @@
         <v>173</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12699,10 +12681,10 @@
         <v>177</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12713,10 +12695,10 @@
         <v>181</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>1237</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12727,10 +12709,10 @@
         <v>185</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>1238</v>
+        <v>1232</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12741,10 +12723,10 @@
         <v>187</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1240</v>
+        <v>1234</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>1241</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12755,10 +12737,10 @@
         <v>191</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12769,10 +12751,10 @@
         <v>193</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1244</v>
+        <v>1238</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>1245</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12783,10 +12765,10 @@
         <v>197</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>1247</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12797,10 +12779,10 @@
         <v>199</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1248</v>
+        <v>1242</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>1249</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12811,10 +12793,10 @@
         <v>201</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>1250</v>
+        <v>1244</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12825,10 +12807,10 @@
         <v>205</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1252</v>
+        <v>1246</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12839,10 +12821,10 @@
         <v>209</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12853,10 +12835,10 @@
         <v>213</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12867,10 +12849,10 @@
         <v>217</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12881,10 +12863,10 @@
         <v>221</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12895,10 +12877,10 @@
         <v>225</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12909,10 +12891,10 @@
         <v>229</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12923,10 +12905,10 @@
         <v>233</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12937,10 +12919,10 @@
         <v>237</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12951,10 +12933,10 @@
         <v>241</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12965,10 +12947,10 @@
         <v>245</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12979,10 +12961,10 @@
         <v>249</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -12993,10 +12975,10 @@
         <v>253</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13007,10 +12989,10 @@
         <v>257</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13021,10 +13003,10 @@
         <v>261</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13035,10 +13017,10 @@
         <v>265</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13049,10 +13031,10 @@
         <v>269</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13063,10 +13045,10 @@
         <v>273</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13077,10 +13059,10 @@
         <v>277</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13091,10 +13073,10 @@
         <v>281</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13105,10 +13087,10 @@
         <v>285</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13119,10 +13101,10 @@
         <v>289</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13133,10 +13115,10 @@
         <v>293</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13147,10 +13129,10 @@
         <v>297</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13161,10 +13143,10 @@
         <v>301</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13175,10 +13157,10 @@
         <v>305</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13189,10 +13171,10 @@
         <v>307</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13203,10 +13185,10 @@
         <v>309</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13217,10 +13199,10 @@
         <v>311</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13239,10 +13221,10 @@
         <v>316</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13251,10 +13233,10 @@
       </c>
       <c r="B98" s="11"/>
       <c r="C98" s="5" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>1269</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13265,10 +13247,10 @@
         <v>319</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>1270</v>
+        <v>1264</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>1271</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13279,10 +13261,10 @@
         <v>321</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>1273</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13293,10 +13275,10 @@
         <v>323</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>1274</v>
+        <v>1268</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>1275</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13307,10 +13289,10 @@
         <v>325</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>1276</v>
+        <v>1270</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13321,10 +13303,10 @@
         <v>327</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>1279</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13335,10 +13317,10 @@
         <v>329</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>1280</v>
+        <v>1274</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>1281</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13349,10 +13331,10 @@
         <v>331</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>1282</v>
+        <v>1276</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>1283</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13363,10 +13345,10 @@
         <v>333</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>1284</v>
+        <v>1278</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>1285</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13377,10 +13359,10 @@
         <v>335</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>1286</v>
+        <v>1280</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>1287</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13391,10 +13373,10 @@
         <v>337</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>1288</v>
+        <v>1282</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>1289</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13405,10 +13387,10 @@
         <v>339</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>1290</v>
+        <v>1284</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>1291</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13417,10 +13399,10 @@
       </c>
       <c r="B110" s="11"/>
       <c r="C110" s="5" t="s">
-        <v>1292</v>
+        <v>1286</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13431,10 +13413,10 @@
         <v>342</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>1294</v>
+        <v>1288</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>1295</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13443,10 +13425,10 @@
       </c>
       <c r="B112" s="11"/>
       <c r="C112" s="5" t="s">
-        <v>1296</v>
+        <v>1290</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>1297</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13455,10 +13437,10 @@
       </c>
       <c r="B113" s="10"/>
       <c r="C113" s="2" t="s">
-        <v>1298</v>
+        <v>1292</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>1299</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13469,10 +13451,10 @@
         <v>346</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>1300</v>
+        <v>1294</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>1301</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13483,10 +13465,10 @@
         <v>348</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>1302</v>
+        <v>1296</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13497,10 +13479,10 @@
         <v>350</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>1305</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13511,10 +13493,10 @@
         <v>352</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>1306</v>
+        <v>1300</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>1307</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13539,10 +13521,10 @@
         <v>356</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13553,10 +13535,10 @@
         <v>358</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>1308</v>
+        <v>1302</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>1309</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13567,10 +13549,10 @@
         <v>360</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>1310</v>
+        <v>1304</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>1311</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13581,10 +13563,10 @@
         <v>362</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>1312</v>
+        <v>1306</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>1313</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13595,10 +13577,10 @@
         <v>364</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13609,10 +13591,10 @@
         <v>366</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>1314</v>
+        <v>1308</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>1315</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13623,10 +13605,10 @@
         <v>368</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13635,10 +13617,10 @@
       </c>
       <c r="B126" s="11"/>
       <c r="C126" s="5" t="s">
-        <v>1316</v>
+        <v>1310</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>1317</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13649,10 +13631,10 @@
         <v>371</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>1318</v>
+        <v>1312</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>1319</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13663,10 +13645,10 @@
         <v>373</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>1320</v>
+        <v>1314</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>1321</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13677,10 +13659,10 @@
         <v>375</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13691,10 +13673,10 @@
         <v>377</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>1322</v>
+        <v>1316</v>
       </c>
       <c r="D130" s="7" t="s">
-        <v>1323</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13705,10 +13687,10 @@
         <v>381</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>1324</v>
+        <v>1318</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>1325</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13719,10 +13701,10 @@
         <v>385</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>1326</v>
+        <v>1320</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>1327</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13733,10 +13715,10 @@
         <v>389</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>1328</v>
+        <v>1322</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>1329</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13747,10 +13729,10 @@
         <v>393</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>1331</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13761,10 +13743,10 @@
         <v>397</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>1332</v>
+        <v>1326</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>1333</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13775,10 +13757,10 @@
         <v>400</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>1335</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13789,10 +13771,10 @@
         <v>404</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>1336</v>
+        <v>1330</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>1337</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13803,10 +13785,10 @@
         <v>408</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>1338</v>
+        <v>1332</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>1339</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13817,10 +13799,10 @@
         <v>412</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13831,10 +13813,10 @@
         <v>416</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13845,10 +13827,10 @@
         <v>420</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>1344</v>
+        <v>1338</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13859,10 +13841,10 @@
         <v>424</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13873,10 +13855,10 @@
         <v>428</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13887,10 +13869,10 @@
         <v>432</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="D144" s="7" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13901,10 +13883,10 @@
         <v>436</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13915,10 +13897,10 @@
         <v>438</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>1350</v>
+        <v>1344</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>1351</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13929,10 +13911,10 @@
         <v>440</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>1353</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13943,10 +13925,10 @@
         <v>444</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>1354</v>
+        <v>1348</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>1355</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13957,10 +13939,10 @@
         <v>448</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>1356</v>
+        <v>1350</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>1357</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13971,10 +13953,10 @@
         <v>452</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>1359</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13985,10 +13967,10 @@
         <v>456</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -13999,10 +13981,10 @@
         <v>460</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="D152" s="7" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14013,10 +13995,10 @@
         <v>463</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14027,10 +14009,10 @@
         <v>467</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>1360</v>
+        <v>1354</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>1361</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14041,10 +14023,10 @@
         <v>471</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>1362</v>
+        <v>1356</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>1363</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14055,10 +14037,10 @@
         <v>475</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>1364</v>
+        <v>1358</v>
       </c>
       <c r="D156" s="7" t="s">
-        <v>1365</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14069,10 +14051,10 @@
         <v>479</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>1367</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14083,10 +14065,10 @@
         <v>482</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>1368</v>
+        <v>1362</v>
       </c>
       <c r="D158" s="7" t="s">
-        <v>1369</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14097,10 +14079,10 @@
         <v>484</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>1322</v>
+        <v>1316</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>1323</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14111,10 +14093,10 @@
         <v>486</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14125,10 +14107,10 @@
         <v>490</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>1370</v>
+        <v>1364</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>1371</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14139,10 +14121,10 @@
         <v>494</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>1372</v>
+        <v>1366</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14153,10 +14135,10 @@
         <v>498</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>1374</v>
+        <v>1368</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>1375</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14167,10 +14149,10 @@
         <v>502</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1376</v>
+        <v>1370</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>1377</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14181,10 +14163,10 @@
         <v>506</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>1378</v>
+        <v>1372</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>1379</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14195,10 +14177,10 @@
         <v>510</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1380</v>
+        <v>1374</v>
       </c>
       <c r="D166" s="7" t="s">
-        <v>1381</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14209,10 +14191,10 @@
         <v>514</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>1383</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14223,10 +14205,10 @@
         <v>518</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>1384</v>
+        <v>1378</v>
       </c>
       <c r="D168" s="7" t="s">
-        <v>1385</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14237,10 +14219,10 @@
         <v>522</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>1387</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14251,10 +14233,10 @@
         <v>526</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>1388</v>
+        <v>1382</v>
       </c>
       <c r="D170" s="7" t="s">
-        <v>1389</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14265,10 +14247,10 @@
         <v>530</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>1390</v>
+        <v>1384</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>1391</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14279,10 +14261,10 @@
         <v>534</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>1392</v>
+        <v>1386</v>
       </c>
       <c r="D172" s="7" t="s">
-        <v>1393</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14293,10 +14275,10 @@
         <v>538</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>1394</v>
+        <v>1388</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14307,10 +14289,10 @@
         <v>542</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
       <c r="D174" s="7" t="s">
-        <v>1397</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14321,10 +14303,10 @@
         <v>546</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>1398</v>
+        <v>1392</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>1399</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14335,10 +14317,10 @@
         <v>550</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>1400</v>
+        <v>1394</v>
       </c>
       <c r="D176" s="7" t="s">
-        <v>1401</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14349,10 +14331,10 @@
         <v>554</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>1402</v>
+        <v>1396</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>1403</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14363,10 +14345,10 @@
         <v>558</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>1404</v>
+        <v>1398</v>
       </c>
       <c r="D178" s="7" t="s">
-        <v>1405</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14377,556 +14359,556 @@
         <v>562</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>1407</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B180" s="11" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>1408</v>
+        <v>1402</v>
       </c>
       <c r="D180" s="7" t="s">
-        <v>1409</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>1411</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="5" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="B182" s="11" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>1412</v>
+        <v>1406</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>1413</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="5" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="B184" s="11" t="s">
         <v>450</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>1416</v>
+        <v>1410</v>
       </c>
       <c r="D184" s="7" t="s">
-        <v>1417</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>1418</v>
+        <v>1412</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>1419</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="5" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="B186" s="11" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>1420</v>
+        <v>1414</v>
       </c>
       <c r="D186" s="7" t="s">
-        <v>1421</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>1422</v>
+        <v>1416</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>1423</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="5" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>1424</v>
+        <v>1418</v>
       </c>
       <c r="D188" s="7" t="s">
-        <v>1425</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>1426</v>
+        <v>1420</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="5" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="B190" s="11" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>1428</v>
+        <v>1422</v>
       </c>
       <c r="D190" s="7" t="s">
-        <v>1429</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="2" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>1431</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="5" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B192" s="11" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>1432</v>
+        <v>1426</v>
       </c>
       <c r="D192" s="7" t="s">
-        <v>1433</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="5" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="B194" s="11" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="D194" s="7" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="B195" s="10" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="5" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="B196" s="11" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="D196" s="7" t="s">
-        <v>1441</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B197" s="10" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>1442</v>
+        <v>1436</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="5" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B198" s="11" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="D198" s="7" t="s">
-        <v>1445</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="B199" s="10" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="5" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="B200" s="11" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="D200" s="7" t="s">
-        <v>1447</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="B201" s="10" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="5" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="B202" s="11" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>1448</v>
+        <v>1442</v>
       </c>
       <c r="D202" s="7" t="s">
-        <v>1449</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="B203" s="10" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="5" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="B204" s="11" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="D204" s="7" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="B205" s="10" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>1450</v>
+        <v>1444</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>1451</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="5" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="B206" s="11" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>1452</v>
+        <v>1446</v>
       </c>
       <c r="D206" s="7" t="s">
-        <v>1453</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="B207" s="10" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>1454</v>
+        <v>1448</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>1455</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="5" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="B208" s="11" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>1456</v>
+        <v>1450</v>
       </c>
       <c r="D208" s="7" t="s">
-        <v>1457</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="B209" s="10" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="5" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="B210" s="11" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>1458</v>
+        <v>1452</v>
       </c>
       <c r="D210" s="7" t="s">
-        <v>1459</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="B211" s="10" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="5" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="B212" s="11" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="D212" s="7" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="B213" s="10" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>1465</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="5" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="B214" s="11" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>1466</v>
+        <v>1460</v>
       </c>
       <c r="D214" s="7" t="s">
-        <v>1467</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="B215" s="10" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>1468</v>
+        <v>1462</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>1469</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="5" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="B216" s="11" t="s">
         <v>465</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>1470</v>
+        <v>1464</v>
       </c>
       <c r="D216" s="7" t="s">
-        <v>1471</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="B217" s="10" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="5" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="B218" s="11" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>1474</v>
+        <v>1468</v>
       </c>
       <c r="D218" s="7" t="s">
-        <v>1475</v>
+        <v>1469</v>
       </c>
     </row>
   </sheetData>
@@ -14953,7 +14935,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1476</v>
+        <v>1470</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -14970,10 +14952,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1477</v>
+        <v>1471</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1478</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14984,10 +14966,10 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1479</v>
+        <v>1473</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>1480</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -14998,10 +14980,10 @@
         <v>11</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1481</v>
+        <v>1475</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1482</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15012,10 +14994,10 @@
         <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1483</v>
+        <v>1477</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>1484</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15026,10 +15008,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15037,13 +15019,13 @@
         <v>18</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>1946</v>
+        <v>1940</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>1488</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15054,10 +15036,10 @@
         <v>21</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1489</v>
+        <v>1483</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15068,10 +15050,10 @@
         <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1492</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15082,10 +15064,10 @@
         <v>27</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1493</v>
+        <v>1487</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1494</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15096,10 +15078,10 @@
         <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1495</v>
+        <v>1489</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1496</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15110,10 +15092,10 @@
         <v>33</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1498</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15124,10 +15106,10 @@
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1499</v>
+        <v>1493</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>1500</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15138,10 +15120,10 @@
         <v>37</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1501</v>
+        <v>1495</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1502</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15152,10 +15134,10 @@
         <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1503</v>
+        <v>1497</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>1504</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15166,10 +15148,10 @@
         <v>43</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1505</v>
+        <v>1499</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1506</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15180,10 +15162,10 @@
         <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1507</v>
+        <v>1501</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1508</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15194,10 +15176,10 @@
         <v>47</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>1509</v>
+        <v>1503</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1510</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15208,10 +15190,10 @@
         <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1511</v>
+        <v>1505</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>1512</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15222,10 +15204,10 @@
         <v>51</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>1513</v>
+        <v>1507</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1514</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15236,10 +15218,10 @@
         <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1515</v>
+        <v>1509</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>1516</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15250,10 +15232,10 @@
         <v>55</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>1517</v>
+        <v>1511</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1518</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15264,10 +15246,10 @@
         <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1519</v>
+        <v>1513</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>1520</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15278,10 +15260,10 @@
         <v>59</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>1521</v>
+        <v>1515</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1522</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15292,10 +15274,10 @@
         <v>61</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1523</v>
+        <v>1517</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>1524</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15306,10 +15288,10 @@
         <v>63</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>1525</v>
+        <v>1519</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1526</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15320,10 +15302,10 @@
         <v>65</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1527</v>
+        <v>1521</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>1528</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15334,10 +15316,10 @@
         <v>67</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>1529</v>
+        <v>1523</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1530</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15348,10 +15330,10 @@
         <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15362,10 +15344,10 @@
         <v>71</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15376,10 +15358,10 @@
         <v>73</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1535</v>
+        <v>1529</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>1536</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15390,10 +15372,10 @@
         <v>75</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>1537</v>
+        <v>1531</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1538</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15404,10 +15386,10 @@
         <v>77</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1539</v>
+        <v>1533</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>1540</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15418,10 +15400,10 @@
         <v>81</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>1541</v>
+        <v>1535</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1542</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15432,10 +15414,10 @@
         <v>85</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1543</v>
+        <v>1537</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>1544</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15446,10 +15428,10 @@
         <v>89</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>1545</v>
+        <v>1539</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1546</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15460,10 +15442,10 @@
         <v>93</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1547</v>
+        <v>1541</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>1548</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15474,10 +15456,10 @@
         <v>97</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1550</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15488,10 +15470,10 @@
         <v>101</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1551</v>
+        <v>1545</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>1552</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15502,10 +15484,10 @@
         <v>105</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>1553</v>
+        <v>1547</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15516,10 +15498,10 @@
         <v>109</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>1556</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15530,10 +15512,10 @@
         <v>113</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1558</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15544,10 +15526,10 @@
         <v>117</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1559</v>
+        <v>1553</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>1560</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15558,10 +15540,10 @@
         <v>121</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>1561</v>
+        <v>1555</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1562</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15572,10 +15554,10 @@
         <v>125</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1563</v>
+        <v>1557</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>1564</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15586,10 +15568,10 @@
         <v>129</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>1565</v>
+        <v>1559</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>1566</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15600,10 +15582,10 @@
         <v>133</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15614,10 +15596,10 @@
         <v>137</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1570</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15628,10 +15610,10 @@
         <v>141</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1571</v>
+        <v>1565</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>1572</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15642,10 +15624,10 @@
         <v>145</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>1573</v>
+        <v>1567</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1574</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15656,10 +15638,10 @@
         <v>149</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1575</v>
+        <v>1569</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>1576</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15670,10 +15652,10 @@
         <v>153</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>1577</v>
+        <v>1571</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1578</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15684,10 +15666,10 @@
         <v>157</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>1579</v>
+        <v>1573</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>1580</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15698,10 +15680,10 @@
         <v>161</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>1581</v>
+        <v>1575</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1582</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15712,10 +15694,10 @@
         <v>165</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>1584</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15726,10 +15708,10 @@
         <v>169</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>1585</v>
+        <v>1579</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1586</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15740,10 +15722,10 @@
         <v>173</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1587</v>
+        <v>1581</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>1588</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15754,10 +15736,10 @@
         <v>177</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>1589</v>
+        <v>1583</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1590</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15768,10 +15750,10 @@
         <v>181</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1591</v>
+        <v>1585</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15782,10 +15764,10 @@
         <v>185</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>1593</v>
+        <v>1587</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1594</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15796,10 +15778,10 @@
         <v>187</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1595</v>
+        <v>1589</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>1596</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15810,10 +15792,10 @@
         <v>191</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>1597</v>
+        <v>1591</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>1598</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15824,10 +15806,10 @@
         <v>193</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1599</v>
+        <v>1593</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>1600</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15838,10 +15820,10 @@
         <v>197</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>1601</v>
+        <v>1595</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>1602</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15852,10 +15834,10 @@
         <v>199</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1603</v>
+        <v>1597</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>1604</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15866,10 +15848,10 @@
         <v>201</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>1605</v>
+        <v>1599</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>1606</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15880,10 +15862,10 @@
         <v>205</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1607</v>
+        <v>1601</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1608</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15894,10 +15876,10 @@
         <v>209</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>1609</v>
+        <v>1603</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>1610</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15908,10 +15890,10 @@
         <v>213</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1611</v>
+        <v>1605</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>1612</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15922,10 +15904,10 @@
         <v>217</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>1613</v>
+        <v>1607</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>1614</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -15992,10 +15974,10 @@
         <v>237</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1615</v>
+        <v>1609</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>1616</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16006,10 +15988,10 @@
         <v>241</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>1617</v>
+        <v>1611</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>1618</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16020,10 +16002,10 @@
         <v>245</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>1619</v>
+        <v>1613</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>1620</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16034,10 +16016,10 @@
         <v>249</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>1621</v>
+        <v>1615</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>1622</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16048,10 +16030,10 @@
         <v>253</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>1623</v>
+        <v>1617</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>1624</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16062,10 +16044,10 @@
         <v>257</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>1625</v>
+        <v>1619</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>1626</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16076,10 +16058,10 @@
         <v>261</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>1627</v>
+        <v>1621</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>1628</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16090,10 +16072,10 @@
         <v>265</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>1629</v>
+        <v>1623</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>1630</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16104,10 +16086,10 @@
         <v>269</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>1631</v>
+        <v>1625</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16118,10 +16100,10 @@
         <v>273</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>1633</v>
+        <v>1627</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>1634</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16132,10 +16114,10 @@
         <v>277</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>1635</v>
+        <v>1629</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>1636</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16146,10 +16128,10 @@
         <v>281</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>1637</v>
+        <v>1631</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>1638</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16160,10 +16142,10 @@
         <v>285</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>1639</v>
+        <v>1633</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>1640</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16174,10 +16156,10 @@
         <v>289</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>1641</v>
+        <v>1635</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>1642</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16188,10 +16170,10 @@
         <v>293</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>1643</v>
+        <v>1637</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>1644</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16202,10 +16184,10 @@
         <v>297</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>1645</v>
+        <v>1639</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>1646</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16216,10 +16198,10 @@
         <v>301</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>1647</v>
+        <v>1641</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>1648</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16230,10 +16212,10 @@
         <v>305</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>1649</v>
+        <v>1643</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>1650</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16244,10 +16226,10 @@
         <v>307</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>1651</v>
+        <v>1645</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>1652</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16258,10 +16240,10 @@
         <v>309</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>1653</v>
+        <v>1647</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>1654</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16272,10 +16254,10 @@
         <v>311</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>1655</v>
+        <v>1649</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>1656</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16286,10 +16268,10 @@
         <v>316</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>1657</v>
+        <v>1651</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>1658</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16298,10 +16280,10 @@
       </c>
       <c r="B97" s="13"/>
       <c r="C97" s="5" t="s">
-        <v>1627</v>
+        <v>1621</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>1628</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16312,10 +16294,10 @@
         <v>319</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>1629</v>
+        <v>1623</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>1630</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16326,10 +16308,10 @@
         <v>321</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>1659</v>
+        <v>1653</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>1660</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16340,10 +16322,10 @@
         <v>323</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>1661</v>
+        <v>1655</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>1662</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16354,10 +16336,10 @@
         <v>325</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>1663</v>
+        <v>1657</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>1664</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16368,10 +16350,10 @@
         <v>327</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>1665</v>
+        <v>1659</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>1666</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16382,10 +16364,10 @@
         <v>329</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>1667</v>
+        <v>1661</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>1668</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16396,10 +16378,10 @@
         <v>331</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>1669</v>
+        <v>1663</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>1670</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16410,10 +16392,10 @@
         <v>333</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>1671</v>
+        <v>1665</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>1672</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16424,10 +16406,10 @@
         <v>335</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>1673</v>
+        <v>1667</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>1674</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16438,10 +16420,10 @@
         <v>337</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>1675</v>
+        <v>1669</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>1676</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16452,10 +16434,10 @@
         <v>339</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>1677</v>
+        <v>1671</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>1678</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16463,13 +16445,13 @@
         <v>340</v>
       </c>
       <c r="B109" s="28" t="s">
-        <v>1936</v>
+        <v>1930</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>1679</v>
+        <v>1673</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>1680</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16480,10 +16462,10 @@
         <v>342</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>1681</v>
+        <v>1675</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>1682</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16491,13 +16473,13 @@
         <v>343</v>
       </c>
       <c r="B111" s="28" t="s">
-        <v>1937</v>
+        <v>1931</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>1683</v>
+        <v>1677</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>1684</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16505,13 +16487,13 @@
         <v>344</v>
       </c>
       <c r="B112" s="29" t="s">
-        <v>1938</v>
+        <v>1932</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>1685</v>
+        <v>1679</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>1686</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16522,10 +16504,10 @@
         <v>346</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>1687</v>
+        <v>1681</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>1688</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16536,10 +16518,10 @@
         <v>348</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>1689</v>
+        <v>1683</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>1690</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16550,10 +16532,10 @@
         <v>350</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>1691</v>
+        <v>1685</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>1692</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16564,10 +16546,10 @@
         <v>352</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>1693</v>
+        <v>1687</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>1694</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16578,10 +16560,10 @@
         <v>354</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>1695</v>
+        <v>1689</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>1696</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16592,10 +16574,10 @@
         <v>356</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>1697</v>
+        <v>1691</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>1698</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16606,10 +16588,10 @@
         <v>358</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>1699</v>
+        <v>1693</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>1700</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16620,10 +16602,10 @@
         <v>360</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>1701</v>
+        <v>1695</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>1702</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16631,13 +16613,13 @@
         <v>361</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>1883</v>
+        <v>1877</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>1703</v>
+        <v>1697</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>1704</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16648,10 +16630,10 @@
         <v>364</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>1705</v>
+        <v>1699</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>1706</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16662,10 +16644,10 @@
         <v>366</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>1707</v>
+        <v>1701</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>1708</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16676,10 +16658,10 @@
         <v>368</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>1709</v>
+        <v>1703</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>1710</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16687,13 +16669,13 @@
         <v>369</v>
       </c>
       <c r="B125" s="28" t="s">
-        <v>1939</v>
+        <v>1933</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>1711</v>
+        <v>1705</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>1712</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16704,10 +16686,10 @@
         <v>371</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>1713</v>
+        <v>1707</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>1714</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16718,10 +16700,10 @@
         <v>373</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>1715</v>
+        <v>1709</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>1716</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16732,10 +16714,10 @@
         <v>375</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>1717</v>
+        <v>1711</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>1718</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16746,10 +16728,10 @@
         <v>377</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>1719</v>
+        <v>1713</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>1720</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16760,10 +16742,10 @@
         <v>381</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>1721</v>
+        <v>1715</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>1722</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16774,10 +16756,10 @@
         <v>385</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>1723</v>
+        <v>1717</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>1724</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16788,10 +16770,10 @@
         <v>389</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>1725</v>
+        <v>1719</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>1726</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16802,10 +16784,10 @@
         <v>393</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>1727</v>
+        <v>1721</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>1728</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16816,10 +16798,10 @@
         <v>397</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>1729</v>
+        <v>1723</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>1730</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16830,10 +16812,10 @@
         <v>400</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>1731</v>
+        <v>1725</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>1732</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16844,10 +16826,10 @@
         <v>404</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>1733</v>
+        <v>1727</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>1734</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16858,10 +16840,10 @@
         <v>408</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>1735</v>
+        <v>1729</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>1736</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16872,10 +16854,10 @@
         <v>412</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>1737</v>
+        <v>1731</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>1738</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16886,10 +16868,10 @@
         <v>416</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>1739</v>
+        <v>1733</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>1740</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16900,10 +16882,10 @@
         <v>420</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>1741</v>
+        <v>1735</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>1742</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16914,10 +16896,10 @@
         <v>424</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>1743</v>
+        <v>1737</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>1744</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16928,10 +16910,10 @@
         <v>428</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>1745</v>
+        <v>1739</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>1746</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16942,10 +16924,10 @@
         <v>432</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>1747</v>
+        <v>1741</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>1748</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16956,10 +16938,10 @@
         <v>436</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>1749</v>
+        <v>1743</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>1750</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16970,10 +16952,10 @@
         <v>438</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>1751</v>
+        <v>1745</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>1752</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16984,10 +16966,10 @@
         <v>440</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>1753</v>
+        <v>1747</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>1754</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -16998,10 +16980,10 @@
         <v>444</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>1755</v>
+        <v>1749</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>1756</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17012,10 +16994,10 @@
         <v>448</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>1757</v>
+        <v>1751</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>1758</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17026,10 +17008,10 @@
         <v>452</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>1759</v>
+        <v>1753</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17040,10 +17022,10 @@
         <v>456</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>1761</v>
+        <v>1755</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>1762</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17054,10 +17036,10 @@
         <v>460</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>1763</v>
+        <v>1757</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>1764</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17068,10 +17050,10 @@
         <v>463</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>1765</v>
+        <v>1759</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>1766</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17082,10 +17064,10 @@
         <v>467</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>1767</v>
+        <v>1761</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>1768</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17096,10 +17078,10 @@
         <v>471</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>1769</v>
+        <v>1763</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>1770</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17110,10 +17092,10 @@
         <v>475</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>1771</v>
+        <v>1765</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>1772</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17124,10 +17106,10 @@
         <v>479</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>1773</v>
+        <v>1767</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>1774</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17138,10 +17120,10 @@
         <v>482</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>1775</v>
+        <v>1769</v>
       </c>
       <c r="D157" s="7" t="s">
-        <v>1776</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17152,10 +17134,10 @@
         <v>484</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>1777</v>
+        <v>1771</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>1778</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17166,10 +17148,10 @@
         <v>486</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>1779</v>
+        <v>1773</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>1780</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17180,10 +17162,10 @@
         <v>490</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>1781</v>
+        <v>1775</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>1782</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17194,10 +17176,10 @@
         <v>494</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>1783</v>
+        <v>1777</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>1784</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17208,10 +17190,10 @@
         <v>498</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>1785</v>
+        <v>1779</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>1786</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17222,10 +17204,10 @@
         <v>502</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>1787</v>
+        <v>1781</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>1788</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17236,10 +17218,10 @@
         <v>506</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>1789</v>
+        <v>1783</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>1790</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17250,10 +17232,10 @@
         <v>510</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1791</v>
+        <v>1785</v>
       </c>
       <c r="D165" s="7" t="s">
-        <v>1792</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17264,10 +17246,10 @@
         <v>514</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>1793</v>
+        <v>1787</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>1794</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17278,10 +17260,10 @@
         <v>518</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1795</v>
+        <v>1789</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>1796</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17292,10 +17274,10 @@
         <v>522</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>1797</v>
+        <v>1791</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>1798</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17306,10 +17288,10 @@
         <v>526</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1799</v>
+        <v>1793</v>
       </c>
       <c r="D169" s="7" t="s">
-        <v>1800</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17320,10 +17302,10 @@
         <v>530</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>1801</v>
+        <v>1795</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>1802</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17334,10 +17316,10 @@
         <v>534</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>1803</v>
+        <v>1797</v>
       </c>
       <c r="D171" s="7" t="s">
-        <v>1804</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17348,10 +17330,10 @@
         <v>538</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>1805</v>
+        <v>1799</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>1806</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17362,10 +17344,10 @@
         <v>542</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>1807</v>
+        <v>1801</v>
       </c>
       <c r="D173" s="7" t="s">
-        <v>1808</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17376,10 +17358,10 @@
         <v>546</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>1809</v>
+        <v>1803</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>1810</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17390,10 +17372,10 @@
         <v>550</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>1811</v>
+        <v>1805</v>
       </c>
       <c r="D175" s="7" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17404,10 +17386,10 @@
         <v>554</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>1813</v>
+        <v>1807</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17418,10 +17400,10 @@
         <v>558</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>1815</v>
+        <v>1809</v>
       </c>
       <c r="D177" s="7" t="s">
-        <v>1816</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -17432,430 +17414,430 @@
         <v>562</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>1817</v>
+        <v>1811</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>1818</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B179" s="13" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>1819</v>
+        <v>1813</v>
       </c>
       <c r="D179" s="7" t="s">
-        <v>1820</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>1821</v>
+        <v>1815</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>1822</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="5" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="B181" s="13" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>1823</v>
+        <v>1817</v>
       </c>
       <c r="D181" s="7" t="s">
-        <v>1824</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="B182" s="12" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>1825</v>
+        <v>1819</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>1826</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="5" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="B183" s="13" t="s">
         <v>450</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>1827</v>
+        <v>1821</v>
       </c>
       <c r="D183" s="7" t="s">
-        <v>1828</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="B184" s="12" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>1829</v>
+        <v>1823</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>1830</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="5" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="B185" s="13" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>1831</v>
+        <v>1825</v>
       </c>
       <c r="D185" s="7" t="s">
-        <v>1832</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="B186" s="12" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>1833</v>
+        <v>1827</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>1834</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="5" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B187" s="13" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>1835</v>
+        <v>1829</v>
       </c>
       <c r="D187" s="7" t="s">
-        <v>1836</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="B188" s="12" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>1837</v>
+        <v>1831</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>1838</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="5" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="B189" s="13" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>1839</v>
+        <v>1833</v>
       </c>
       <c r="D189" s="7" t="s">
-        <v>1840</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="B190" s="12" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>1841</v>
+        <v>1835</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>1842</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="5" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B191" s="13" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>1843</v>
+        <v>1837</v>
       </c>
       <c r="D191" s="7" t="s">
-        <v>1844</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="B192" s="12" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>1845</v>
+        <v>1839</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>1846</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="5" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="B193" s="13" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>1847</v>
+        <v>1841</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>1848</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="B194" s="12" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>1849</v>
+        <v>1843</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>1850</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="5" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="B195" s="13" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>1851</v>
+        <v>1845</v>
       </c>
       <c r="D195" s="7" t="s">
-        <v>1852</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B196" s="12" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>1853</v>
+        <v>1847</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>1854</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="5" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B197" s="13" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>1855</v>
+        <v>1849</v>
       </c>
       <c r="D197" s="7" t="s">
-        <v>1856</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="B198" s="12" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>1857</v>
+        <v>1851</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>1858</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="5" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="B199" s="13" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>1859</v>
+        <v>1853</v>
       </c>
       <c r="D199" s="7" t="s">
-        <v>1860</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="B200" s="12" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>1861</v>
+        <v>1855</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>1862</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="5" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="B201" s="13" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>1863</v>
+        <v>1857</v>
       </c>
       <c r="D201" s="7" t="s">
-        <v>1864</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="B202" s="12" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>1865</v>
+        <v>1859</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>1866</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="5" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="B203" s="13" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>1867</v>
+        <v>1861</v>
       </c>
       <c r="D203" s="7" t="s">
-        <v>1868</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="B204" s="12" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>1869</v>
+        <v>1863</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>1870</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="5" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="B205" s="13" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>1871</v>
+        <v>1865</v>
       </c>
       <c r="D205" s="7" t="s">
-        <v>1872</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="B206" s="12" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>1873</v>
+        <v>1867</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>1874</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="5" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="B207" s="13" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>1875</v>
+        <v>1869</v>
       </c>
       <c r="D207" s="7" t="s">
-        <v>1876</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="B208" s="12" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>1877</v>
+        <v>1871</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>1878</v>
+        <v>1872</v>
       </c>
     </row>
   </sheetData>
